--- a/data/analysis/commuta_section4_medians.xlsx
+++ b/data/analysis/commuta_section4_medians.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/CASA202526/Dissertation/Commuta_PortableAirMonitor/data/analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667DE2CF-98FA-2A46-A120-5779FA6C38CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DEC9C67-9F66-524F-AC70-14749CA3E6E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,9 +25,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
   <si>
-    <t>Table A1.  Platform PM₂.₅ median by London Underground line</t>
-  </si>
-  <si>
     <t>Line</t>
   </si>
   <si>
@@ -77,9 +74,6 @@
   </si>
   <si>
     <t>Median of 10-second platform samples (µg/m³), rounded to 1 dp; per-station values pool the busier and quieter sessions. Source: commuta_analysis.csv (row-level platform data).</t>
-  </si>
-  <si>
-    <t>Table A2.  Platform PM₂.₅ median by platform environment (all lines pooled)</t>
   </si>
   <si>
     <t>Platform environment</t>
@@ -265,6 +259,102 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> median by station (route order, Bond Street → Stratford)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Platform PM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₅</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> median by London Underground line</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Platform PM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₂</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>₅</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF2A2A2A"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> median by platform environment (all lines pooled)</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -850,32 +940,32 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="5">
         <v>212.6</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6">
         <v>316</v>
@@ -883,13 +973,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="5">
         <v>193.3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="6">
         <v>185</v>
@@ -897,13 +987,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5">
         <v>119.5</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6">
         <v>392</v>
@@ -911,13 +1001,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="5">
         <v>36</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="6">
         <v>394</v>
@@ -925,13 +1015,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5">
         <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="6">
         <v>313</v>
@@ -939,13 +1029,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="12">
         <v>17.8</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="13">
         <v>349</v>
@@ -953,7 +1043,7 @@
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1">
       <c r="A11" s="27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
@@ -980,23 +1070,23 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5">
         <v>6.5</v>
@@ -1007,7 +1097,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="5">
         <v>21.7</v>
@@ -1018,7 +1108,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="5">
         <v>40.9</v>
@@ -1029,7 +1119,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B7" s="5">
         <v>42.6</v>
@@ -1040,7 +1130,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B8" s="12">
         <v>139.30000000000001</v>
@@ -1051,7 +1141,7 @@
     </row>
     <row r="10" spans="1:3" ht="44" customHeight="1">
       <c r="A10" s="27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
@@ -1077,29 +1167,29 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C4" s="6">
         <v>78.3</v>
@@ -1110,10 +1200,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C5" s="6">
         <v>66.8</v>
@@ -1124,10 +1214,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="6">
         <v>50.2</v>
@@ -1138,10 +1228,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C7" s="6">
         <v>64.3</v>
@@ -1152,10 +1242,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="19" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C8" s="6">
         <v>42.5</v>
@@ -1166,10 +1256,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="6">
         <v>43.4</v>
@@ -1180,10 +1270,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="6">
         <v>17.2</v>
@@ -1194,10 +1284,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="19" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="6">
         <v>34.799999999999997</v>
@@ -1208,10 +1298,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="6">
         <v>43.6</v>
@@ -1222,10 +1312,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6">
         <v>9.1999999999999993</v>
@@ -1236,10 +1326,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B14" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" s="6">
         <v>3.2</v>
@@ -1250,10 +1340,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" s="6">
         <v>4.8</v>
@@ -1264,10 +1354,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="23" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="13">
         <v>2.9</v>
@@ -1278,7 +1368,7 @@
     </row>
     <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
@@ -1305,7 +1395,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="102" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B1" s="29"/>
       <c r="C1" s="29"/>
@@ -1313,24 +1403,24 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="6">
         <v>11.2</v>
@@ -1341,10 +1431,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C5" s="6">
         <v>13.4</v>
@@ -1355,10 +1445,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="6">
         <v>54.3</v>
@@ -1369,10 +1459,10 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="6">
         <v>58</v>
@@ -1383,10 +1473,10 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="19" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8" s="6">
         <v>92.1</v>
@@ -1397,10 +1487,10 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="19" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C9" s="6">
         <v>69.400000000000006</v>
@@ -1411,10 +1501,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="19" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="6">
         <v>16.5</v>
@@ -1425,10 +1515,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="19" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6">
         <v>13.3</v>
@@ -1439,10 +1529,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" s="6">
         <v>67.7</v>
@@ -1453,10 +1543,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="13">
         <v>14.5</v>
@@ -1467,7 +1557,7 @@
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1">
       <c r="A15" s="27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
